--- a/templates/2027/blank/03_攤位資料.xlsx
+++ b/templates/2027/blank/03_攤位資料.xlsx
@@ -23,7 +23,10 @@
           <t xml:space="preserve">必須 — 冇就唔成立
 型別：text
 例：A01
-唯一鍵。場地圖同遊戲卡認呢個</t>
+唯一鍵。場地圖同遊戲卡認呢個
+只准填編號本身：一個英文區碼 ＋ 兩位數字。攤位名稱填落「攤位名稱」嗰欄。
+✓ 可以：A01、B07、E12
+✗ 唔好：A1（唔夠兩位）、A1 Core（夾埋名）、A-01（有符號）</t>
         </r>
       </text>
     </comment>
@@ -88,7 +91,10 @@
         <r>
           <t xml:space="preserve">盡量 — 填得幾多得幾多
 型別：number
-例：7</t>
+例：7
+只准填整數。唔好填「7.0」「約7」「7人」。
+✓ 可以：7、0
+✗ 唔好：7.0、約7、7人、七</t>
         </r>
       </text>
     </comment>
@@ -98,7 +104,10 @@
           <t xml:space="preserve">盡量 — 填得幾多得幾多
 型別：number
 例：7
-影響代訂餐盒</t>
+影響代訂餐盒
+只准填整數。唔好填「7.0」「約7」「7人」。
+✓ 可以：7、0
+✗ 唔好：7.0、約7、7人、七</t>
         </r>
       </text>
     </comment>
@@ -107,7 +116,10 @@
         <r>
           <t xml:space="preserve">盡量 — 填得幾多得幾多
 型別：bool
-例：Y</t>
+例：Y
+只准填 Y 或者留空。唔好填「是」「有」「✓」「1」。
+✓ 可以：Y、（留空）
+✗ 唔好：是、有、✓、1、TRUE</t>
         </r>
       </text>
     </comment>
@@ -214,7 +226,7 @@
     <t>級別</t>
   </si>
   <si>
-    <t>型別</t>
+    <t>格式</t>
   </si>
   <si>
     <t>例子</t>
@@ -226,18 +238,18 @@
     <t>A</t>
   </si>
   <si>
+    <t>A01</t>
+  </si>
+  <si>
+    <t>只准填編號本身：一個英文區碼 ＋ 兩位數字。攤位名稱填落「攤位名稱」嗰欄。　✓A01／B07／E12　✗A1（唔夠兩位）／A1 Core（夾埋名）／A-01（有符號）　唯一鍵。場地圖同遊戲卡認呢個</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
     <t>text</t>
   </si>
   <si>
-    <t>A01</t>
-  </si>
-  <si>
-    <t>唯一鍵。場地圖同遊戲卡認呢個</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
     <t>由攤位編號第一個字自動取</t>
   </si>
   <si>
@@ -277,25 +289,25 @@
     <t>H</t>
   </si>
   <si>
-    <t>number</t>
-  </si>
-  <si>
     <t>7</t>
   </si>
   <si>
+    <t>只准填整數。唔好填「7.0」「約7」「7人」。　✓7／0　✗7.0／約7／7人／七</t>
+  </si>
+  <si>
     <t>I</t>
   </si>
   <si>
-    <t>影響代訂餐盒</t>
+    <t>只准填整數。唔好填「7.0」「約7」「7人」。　✓7／0　✗7.0／約7／7人／七　影響代訂餐盒</t>
   </si>
   <si>
     <t>J</t>
   </si>
   <si>
-    <t>bool</t>
-  </si>
-  <si>
     <t>Y</t>
+  </si>
+  <si>
+    <t>只准填 Y 或者留空。唔好填「是」「有」「✓」「1」。　✓Y／（留空）　✗是／有／✓／1／TRUE</t>
   </si>
   <si>
     <t>三級意思</t>
@@ -743,7 +755,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J500"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15.6" customWidth="1"/>
@@ -820,8 +832,514 @@
         <v>12</v>
       </c>
     </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="141" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="142" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="143" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="144" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="145" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="146" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="147" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="148" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="149" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="150" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="151" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="152" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="153" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="154" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="155" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="156" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="157" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="158" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="159" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="160" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="161" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="162" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="163" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="164" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="165" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="166" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="167" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="168" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="169" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="170" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="171" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="172" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="173" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="174" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="175" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="176" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="177" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="178" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="179" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="180" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="181" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="182" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="183" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="184" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="185" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="186" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="187" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="188" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="189" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="190" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="191" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="192" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="193" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="194" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="195" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="196" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="197" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="198" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="199" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="200" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="201" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="202" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="203" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="204" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="205" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="206" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="207" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="208" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="209" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="210" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="211" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="212" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="213" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="214" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="215" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="216" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="217" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="218" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="219" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="220" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="221" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="222" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="223" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="224" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="225" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="226" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="227" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="228" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="229" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="230" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="231" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="232" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="233" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="234" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="235" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="236" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="237" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="238" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="239" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="240" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="241" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="242" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="243" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="244" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="245" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="246" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="247" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="248" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="249" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="250" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="251" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="252" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="253" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="254" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="255" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="256" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="257" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="258" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="259" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="260" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="261" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="262" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="263" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="264" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="265" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="266" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="267" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="268" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="269" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="270" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="271" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="272" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="273" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="274" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="275" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="276" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="277" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="278" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="279" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="280" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="281" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="282" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="283" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="284" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="285" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="286" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="287" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="288" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="289" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="290" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="291" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="292" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="293" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="294" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="295" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="296" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="297" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="298" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="299" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="300" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="301" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="302" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="303" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="304" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="305" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="306" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="307" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="308" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="309" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="310" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="311" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="312" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="313" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="314" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="315" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="316" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="317" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="318" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="319" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="320" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="321" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="322" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="323" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="324" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="325" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="326" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="327" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="328" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="329" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="330" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="331" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="332" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="333" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="334" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="335" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="336" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="337" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="338" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="339" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="340" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="341" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="342" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="343" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="344" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="345" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="346" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="347" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="348" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="349" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="350" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="351" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="352" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="353" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="354" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="355" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="356" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="357" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="358" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="359" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="360" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="361" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="362" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="363" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="364" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="365" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="366" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="367" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="368" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="369" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="370" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="371" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="372" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="373" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="374" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="375" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="376" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="377" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="378" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="379" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="380" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="381" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="382" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="383" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="384" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="385" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="386" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="387" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="388" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="389" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="390" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="391" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="392" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="393" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="394" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="395" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="396" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="397" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="398" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="399" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="400" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="401" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="402" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="403" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="404" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="405" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="406" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="407" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="408" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="409" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="410" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="411" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="412" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="413" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="414" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="415" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="416" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="417" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="418" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="419" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="420" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="421" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="422" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="423" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="424" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="425" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="426" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="427" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="428" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="429" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="430" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="431" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="432" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="433" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="434" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="435" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="436" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="437" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="438" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="439" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="440" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="441" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="442" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="443" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="444" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="445" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="446" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="447" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="448" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="449" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="450" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="451" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="452" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="453" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="454" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="455" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="456" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="457" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="458" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="459" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="460" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="461" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="462" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="463" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="464" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="465" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="466" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="467" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="468" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="469" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="470" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="471" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="472" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="473" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="474" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="475" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="476" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="477" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="478" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="479" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="480" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="481" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="482" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="483" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="484" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="485" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="486" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="487" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="488" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="489" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="490" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="491" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="492" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="493" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="494" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="495" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="496" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="497" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="498" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="499" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="500" spans="1:10" x14ac:dyDescent="0.25"/>
   </sheetData>
   <autoFilter ref="A1:J1"/>
+  <dataValidations count="6">
+    <dataValidation showInputMessage="1" promptTitle="攤位編號　格式" prompt="只准填編號本身：一個英文區碼 ＋ 兩位數字。攤位名稱填落「攤位名稱」嗰欄。  ✓ 可以：A01、B07、E12 ✗ 唔好：A1（唔夠兩位）、A1 Core（夾埋名）、A-01（有符號）" sqref="A10:A500"/>
+    <dataValidation showInputMessage="1" promptTitle="攤位編號　格式" prompt="只准填編號本身：一個英文區碼 ＋ 兩位數字。攤位名稱填落「攤位名稱」嗰欄。  ✓ 可以：A01、B07、E12 ✗ 唔好：A1（唔夠兩位）、A1 Core（夾埋名）、A-01（有符號）" sqref="A3:A500"/>
+    <dataValidation showInputMessage="1" promptTitle="數目　格式" prompt="只准填整數。唔好填「7.0」「約7」「7人」。  ✓ 可以：7、0 ✗ 唔好：7.0、約7、7人、七" sqref="H10:I500"/>
+    <dataValidation showInputMessage="1" promptTitle="數目　格式" prompt="只准填整數。唔好填「7.0」「約7」「7人」。  ✓ 可以：7、0 ✗ 唔好：7.0、約7、7人、七" sqref="H3:I500"/>
+    <dataValidation showInputMessage="1" promptTitle="是／否　格式" prompt="只准填 Y 或者留空。唔好填「是」「有」「✓」「1」。  ✓ 可以：Y、（留空） ✗ 唔好：是、有、✓、1、TRUE" sqref="J10:J500"/>
+    <dataValidation showInputMessage="1" promptTitle="是／否　格式" prompt="只准填 Y 或者留空。唔好填「是」「有」「✓」「1」。  ✓ 可以：Y、（留空） ✗ 唔好：是、有、✓、1、TRUE" sqref="J3:J500"/>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
   <legacyDrawing r:id="rId2"/>
@@ -938,15 +1456,15 @@
         <v>36</v>
       </c>
       <c r="E12" t="s">
+        <v>36</v>
+      </c>
+      <c r="F12" s="13" t="s">
         <v>37</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B13" t="s">
         <v>1</v>
@@ -955,7 +1473,7 @@
         <v>11</v>
       </c>
       <c r="D13" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E13" t="s">
         <v>35</v>
@@ -975,7 +1493,7 @@
         <v>10</v>
       </c>
       <c r="D14" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E14" t="s">
         <v>42</v>
@@ -995,7 +1513,7 @@
         <v>10</v>
       </c>
       <c r="D15" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E15" t="s">
         <v>44</v>
@@ -1015,7 +1533,7 @@
         <v>12</v>
       </c>
       <c r="D16" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E16" t="s">
         <v>46</v>
@@ -1035,7 +1553,7 @@
         <v>12</v>
       </c>
       <c r="D17" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E17" t="s">
         <v>48</v>
@@ -1055,7 +1573,7 @@
         <v>12</v>
       </c>
       <c r="D18" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E18" t="s">
         <v>50</v>
@@ -1078,10 +1596,10 @@
         <v>53</v>
       </c>
       <c r="E19" t="s">
+        <v>53</v>
+      </c>
+      <c r="F19" s="13" t="s">
         <v>54</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1098,7 +1616,7 @@
         <v>53</v>
       </c>
       <c r="E20" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F20" s="13" t="s">
         <v>56</v>
@@ -1118,10 +1636,10 @@
         <v>58</v>
       </c>
       <c r="E21" t="s">
+        <v>58</v>
+      </c>
+      <c r="F21" s="13" t="s">
         <v>59</v>
-      </c>
-      <c r="F21" s="13" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
